--- a/testData/TC_CreateOpportunity.xlsx
+++ b/testData/TC_CreateOpportunity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B8BA0-13C9-4A69-9E2E-F9D10280121E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{CD007C22-7B62-4230-AD5B-78152CB66B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EB0F82B-EA99-4DE7-A726-39C4A0CC177A}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Primary Contact</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Standard</t>
   </si>
   <si>
-    <t>To be Determined Before Qualify Sales Stage</t>
-  </si>
-  <si>
     <t>Direct</t>
   </si>
   <si>
@@ -117,15 +114,9 @@
     <t>Reseller SE</t>
   </si>
   <si>
-    <t>1P</t>
-  </si>
-  <si>
     <t>Hyperscaler</t>
   </si>
   <si>
-    <t>Azure</t>
-  </si>
-  <si>
     <t>LOGIN</t>
   </si>
   <si>
@@ -135,16 +126,16 @@
     <t>SFDC</t>
   </si>
   <si>
-    <t>Reseller through Distributor</t>
-  </si>
-  <si>
     <t>Distrubutor</t>
   </si>
   <si>
-    <t>AVT Technology Solutions LLC</t>
-  </si>
-  <si>
-    <t>Mathew K</t>
+    <t>test test</t>
+  </si>
+  <si>
+    <t>To be Determined at Qualify Sales Stage</t>
+  </si>
+  <si>
+    <t>Reseller through Dristibutor</t>
   </si>
 </sst>
 </file>
@@ -259,7 +250,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,6 +265,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -283,12 +275,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -571,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.84375" bestFit="1" customWidth="1"/>
@@ -586,7 +574,7 @@
     <col min="10" max="10" width="16.61328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.53515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.53515625" customWidth="1"/>
-    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.61328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.3828125" customWidth="1"/>
     <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.53515625" bestFit="1" customWidth="1"/>
@@ -595,50 +583,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
+      <c r="A1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -663,7 +651,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>13</v>
@@ -675,25 +663,25 @@
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="P3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
@@ -713,20 +701,20 @@
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -736,7 +724,7 @@
       </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="10"/>
+      <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
@@ -755,87 +743,49 @@
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
         <v>36</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="R5" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="2">
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" xr:uid="{656F6157-5602-406C-8892-B4852F1C90DA}"/>
-    <hyperlink ref="A6" r:id="rId2" xr:uid="{68F9D418-FDA5-4D8A-90DE-ECB5BA0AFE4F}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{3F3789E9-47C0-4D26-B7C9-19A31F4ABC25}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{3F3789E9-47C0-4D26-B7C9-19A31F4ABC25}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
